--- a/基礎演習/Chapter09.xlsx
+++ b/基礎演習/Chapter09.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aforce1119-my.sharepoint.com/personal/y_takiguchi_a-force_co_jp/Documents/デスクトップ/研修/2026研修計画/2026研修資料/13_Servlet・JSP/01_基礎/02_練習問題/Chapter09/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\村石 莉彩\Desktop\研修資料\13_Servlet・JSP\1.基礎\演習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="13_ncr:1_{11564356-874B-40DB-997F-7C4E850EF571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18E007B6-FE8E-4F63-9DEE-6F2ED10E0B7E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F1475E-2528-44D6-9D3A-8411E3F0E3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="-6510" windowWidth="9810" windowHeight="15585" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="基礎１" sheetId="2" r:id="rId1"/>
@@ -41,13 +41,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="104">
   <si>
     <t>✅ 基礎問題（5問）</t>
   </si>
   <si>
     <t>1. フォワードの仕組み</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>問題： フォワード（forward）の特徴として 正しくないもの を選んでください。</t>
@@ -135,7 +135,7 @@
   </si>
   <si>
     <t>5. JSPからの画面遷移</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>問題： JSP から forward を行う正しい方法を選んでください。</t>
@@ -217,7 +217,7 @@
     <rPh sb="0" eb="3">
       <t>カンイテキ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>フォームで username を入力し、validate.jsp に送信</t>
@@ -254,7 +254,7 @@
       </rPr>
       <t xml:space="preserve"> 応用問題（5問）</t>
     </r>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>【問題】</t>
@@ -303,21 +303,21 @@
     <rPh sb="2" eb="4">
       <t>ガメン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>【要件】</t>
     <rPh sb="1" eb="3">
       <t>ヨウケン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>【問題】</t>
     <rPh sb="1" eb="3">
       <t>モンダイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>フォワード・インクルード・リダイレクトを使った画面遷移アプリを作成しなさい。</t>
@@ -348,27 +348,27 @@
   </si>
   <si>
     <t>Q1.各画面遷移で forward / redirect のどちらを使うか書きなさい。</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>Q2. DB登録が行われるのはどのタイミングか？</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>Q3. もし「確定 → 完了」を forward にした場合、何が起きるか？</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>Q1.各遷移の方法を答えなさい。</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>Q2. URLが変わるのはどのタイミングか</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>Q3. 「入力 → 確認」を redirect にするとどんな問題が起きるか？</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>会員情報変更機能について、画面遷移を設計しなさい。</t>
@@ -378,7 +378,7 @@
     <rPh sb="15" eb="17">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>リダイレクトを使った画面遷移アプリを作成しなさい。</t>
@@ -391,7 +391,7 @@
     <rPh sb="18" eb="20">
       <t>サクセイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>「送信」ボタンがある画面(index.jsp)</t>
@@ -401,14 +401,14 @@
     <rPh sb="10" eb="12">
       <t>ガメン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>完了画面(done.jsp)</t>
     <rPh sb="0" eb="4">
       <t>カンリョウガメン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>「送信」ボタンを押したら完了画面へ遷移すること。</t>
@@ -424,7 +424,7 @@
     <rPh sb="17" eb="19">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>※画面の内容や項目は自由</t>
@@ -440,19 +440,39 @@
     <rPh sb="10" eb="12">
       <t>ジユウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -525,16 +545,19 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1">
@@ -821,204 +844,219 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE37BBFD-B1F3-4C97-B14A-5A65E5DBE894}">
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:9">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:9">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:9">
       <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
+      <c r="I7" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:9">
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:9">
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:9">
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:9">
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:9">
       <c r="B17" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:9">
       <c r="B18" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:9">
       <c r="B19" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
+      <c r="I19" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="B20" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:9">
       <c r="B21" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:9">
       <c r="B22" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:9">
       <c r="A24" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:9">
       <c r="B25" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:9">
       <c r="B27" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:9">
       <c r="B28" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="29" spans="1:2">
+      <c r="I28" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="B29" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:9">
       <c r="B30" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:9">
       <c r="A32" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:9">
       <c r="B33" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:9">
       <c r="B35" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:9">
       <c r="B36" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:9">
       <c r="B37" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="38" spans="1:2">
+      <c r="I37" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="B38" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:9">
       <c r="A40" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:9">
       <c r="B41" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:9">
       <c r="B43" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:9">
       <c r="B44" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:9">
       <c r="B45" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="46" spans="1:2">
+      <c r="I45" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="B46" s="1" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1062,7 +1100,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1186,7 +1224,7 @@
     </row>
     <row r="29" spans="1:2" s="1" customFormat="1"/>
   </sheetData>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1285,7 +1323,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1374,7 +1412,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1434,7 +1472,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1449,6 +1487,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4f770298-b31c-4238-a90d-db1340869ae4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4ebca473-6c88-4eeb-9b46-7f2093239612" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100D00E93C39DF401468E770D4882DF02E4" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="96f527420be350019f68a523211badd0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4f770298-b31c-4238-a90d-db1340869ae4" xmlns:ns3="4ebca473-6c88-4eeb-9b46-7f2093239612" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="43e7199c2f8c1b8a43238954ae45261b" ns2:_="" ns3:_="">
     <xsd:import namespace="4f770298-b31c-4238-a90d-db1340869ae4"/>
@@ -1655,17 +1704,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4f770298-b31c-4238-a90d-db1340869ae4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4ebca473-6c88-4eeb-9b46-7f2093239612" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDD466A4-E68C-487D-B50D-CD9BB6F63972}">
   <ds:schemaRefs>
@@ -1675,10 +1713,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC94E59D-9800-48D6-9A19-37F16AE9BE8D}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67695040-79B2-417D-B035-75DD04DAF546}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1687,4 +1721,23 @@
     <ds:schemaRef ds:uri="4ebca473-6c88-4eeb-9b46-7f2093239612"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC94E59D-9800-48D6-9A19-37F16AE9BE8D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4f770298-b31c-4238-a90d-db1340869ae4"/>
+    <ds:schemaRef ds:uri="4ebca473-6c88-4eeb-9b46-7f2093239612"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/基礎演習/Chapter09.xlsx
+++ b/基礎演習/Chapter09.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\村石 莉彩\Desktop\研修資料\13_Servlet・JSP\1.基礎\演習\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pleiades-2024-12-java-win-64bit-jre_20250120\workspace\Servlet\基礎演習\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F1475E-2528-44D6-9D3A-8411E3F0E3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{161937FD-7743-43FA-9F71-7F533B27DA49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-6510" windowWidth="9810" windowHeight="15585" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29280" yWindow="-6030" windowWidth="17070" windowHeight="15465" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="基礎１" sheetId="2" r:id="rId1"/>
@@ -41,13 +41,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="108">
   <si>
     <t>✅ 基礎問題（5問）</t>
   </si>
   <si>
     <t>1. フォワードの仕組み</t>
-    <phoneticPr fontId="5"/>
+    <phoneticPr fontId="6"/>
   </si>
   <si>
     <t>問題： フォワード（forward）の特徴として 正しくないもの を選んでください。</t>
@@ -135,7 +135,7 @@
   </si>
   <si>
     <t>5. JSPからの画面遷移</t>
-    <phoneticPr fontId="5"/>
+    <phoneticPr fontId="6"/>
   </si>
   <si>
     <t>問題： JSP から forward を行う正しい方法を選んでください。</t>
@@ -217,7 +217,7 @@
     <rPh sb="0" eb="3">
       <t>カンイテキ</t>
     </rPh>
-    <phoneticPr fontId="5"/>
+    <phoneticPr fontId="6"/>
   </si>
   <si>
     <t>フォームで username を入力し、validate.jsp に送信</t>
@@ -254,7 +254,7 @@
       </rPr>
       <t xml:space="preserve"> 応用問題（5問）</t>
     </r>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>【問題】</t>
@@ -303,21 +303,21 @@
     <rPh sb="2" eb="4">
       <t>ガメン</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>【要件】</t>
     <rPh sb="1" eb="3">
       <t>ヨウケン</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>【問題】</t>
     <rPh sb="1" eb="3">
       <t>モンダイ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>フォワード・インクルード・リダイレクトを使った画面遷移アプリを作成しなさい。</t>
@@ -348,27 +348,27 @@
   </si>
   <si>
     <t>Q1.各画面遷移で forward / redirect のどちらを使うか書きなさい。</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>Q2. DB登録が行われるのはどのタイミングか？</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>Q3. もし「確定 → 完了」を forward にした場合、何が起きるか？</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>Q1.各遷移の方法を答えなさい。</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>Q2. URLが変わるのはどのタイミングか</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>Q3. 「入力 → 確認」を redirect にするとどんな問題が起きるか？</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>会員情報変更機能について、画面遷移を設計しなさい。</t>
@@ -378,7 +378,7 @@
     <rPh sb="15" eb="17">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>リダイレクトを使った画面遷移アプリを作成しなさい。</t>
@@ -391,7 +391,7 @@
     <rPh sb="18" eb="20">
       <t>サクセイ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>「送信」ボタンがある画面(index.jsp)</t>
@@ -401,14 +401,14 @@
     <rPh sb="10" eb="12">
       <t>ガメン</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>完了画面(done.jsp)</t>
     <rPh sb="0" eb="4">
       <t>カンリョウガメン</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>「送信」ボタンを押したら完了画面へ遷移すること。</t>
@@ -424,7 +424,7 @@
     <rPh sb="17" eb="19">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>※画面の内容や項目は自由</t>
@@ -440,31 +440,82 @@
     <rPh sb="10" eb="12">
       <t>ジユウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>C</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>A</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
   </si>
   <si>
     <t>B</t>
-    <phoneticPr fontId="4"/>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>forword</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>redirect</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>完了画面に遷移する前</t>
+    <rPh sb="0" eb="4">
+      <t>カンリョウガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>更新ボタンを押すたびに、何度も同じ注文データがDBに登録されてしまう。</t>
+    <rPh sb="0" eb="2">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ナンド</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>チュウモン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -545,16 +596,19 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1">
@@ -1056,7 +1110,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4"/>
+  <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1100,141 +1154,154 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4"/>
+  <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35A7DF41-A30A-41EE-864F-213184131454}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1">
+    <row r="2" spans="1:7" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1">
+    <row r="3" spans="1:7" s="1" customFormat="1">
       <c r="B3" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1"/>
-    <row r="5" spans="1:2" s="1" customFormat="1">
+    <row r="4" spans="1:7" s="1" customFormat="1"/>
+    <row r="5" spans="1:7" s="1" customFormat="1">
       <c r="B5" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:2" s="1" customFormat="1">
+    <row r="6" spans="1:7" s="1" customFormat="1">
       <c r="B6" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="1" customFormat="1">
+    <row r="7" spans="1:7" s="1" customFormat="1">
       <c r="B7" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" s="1" customFormat="1">
+      <c r="F7" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="1" customFormat="1">
       <c r="B8" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="1" customFormat="1"/>
-    <row r="10" spans="1:2" s="1" customFormat="1">
+    <row r="9" spans="1:7" s="1" customFormat="1"/>
+    <row r="10" spans="1:7" s="1" customFormat="1">
       <c r="A10" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="1" customFormat="1">
+    <row r="11" spans="1:7" s="1" customFormat="1">
       <c r="B11" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:2" s="1" customFormat="1"/>
-    <row r="13" spans="1:2" s="1" customFormat="1">
+    <row r="12" spans="1:7" s="1" customFormat="1"/>
+    <row r="13" spans="1:7" s="1" customFormat="1">
       <c r="B13" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="1" customFormat="1">
+    <row r="14" spans="1:7" s="1" customFormat="1">
       <c r="B14" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" s="1" customFormat="1"/>
-    <row r="16" spans="1:2" s="1" customFormat="1">
+      <c r="G14" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="1" customFormat="1"/>
+    <row r="16" spans="1:7" s="1" customFormat="1">
       <c r="A16" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:2" s="1" customFormat="1">
+    <row r="17" spans="1:7" s="1" customFormat="1">
       <c r="B17" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:2" s="1" customFormat="1"/>
-    <row r="19" spans="1:2" s="1" customFormat="1">
+    <row r="18" spans="1:7" s="1" customFormat="1"/>
+    <row r="19" spans="1:7" s="1" customFormat="1">
       <c r="B19" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:2" s="1" customFormat="1">
+    <row r="20" spans="1:7" s="1" customFormat="1">
       <c r="B20" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:2" s="1" customFormat="1">
+    <row r="21" spans="1:7" s="1" customFormat="1">
       <c r="B21" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" s="1" customFormat="1">
+      <c r="F21" s="5"/>
+      <c r="G21" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="1" customFormat="1">
       <c r="B22" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:2" s="1" customFormat="1"/>
-    <row r="24" spans="1:2" s="1" customFormat="1">
+    <row r="23" spans="1:7" s="1" customFormat="1"/>
+    <row r="24" spans="1:7" s="1" customFormat="1">
       <c r="A24" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:2" s="1" customFormat="1">
+    <row r="25" spans="1:7" s="1" customFormat="1">
       <c r="B25" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:2" s="1" customFormat="1"/>
-    <row r="27" spans="1:2" s="1" customFormat="1">
+    <row r="26" spans="1:7" s="1" customFormat="1"/>
+    <row r="27" spans="1:7" s="1" customFormat="1">
       <c r="B27" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:2" s="1" customFormat="1">
+    <row r="28" spans="1:7" s="1" customFormat="1">
       <c r="B28" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" s="1" customFormat="1"/>
+      <c r="G28" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="1" customFormat="1"/>
   </sheetData>
-  <phoneticPr fontId="4"/>
+  <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFDCD669-90AC-46A3-A557-169BBB1820D5}">
-  <dimension ref="B2:C20"/>
+  <dimension ref="B2:J20"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:10">
       <c r="B2" t="s">
         <v>79</v>
       </c>
@@ -1242,88 +1309,106 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="2:10">
       <c r="C3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="2:3">
+    <row r="4" spans="2:10">
       <c r="C4" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="5" spans="2:3">
+      <c r="J4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10">
       <c r="C5" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="7" spans="2:3">
+      <c r="J5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
       <c r="B7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="2:3">
+    <row r="8" spans="2:10">
       <c r="C8" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="2:3">
+    <row r="9" spans="2:10">
       <c r="C9" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="2:3">
+    <row r="10" spans="2:10">
       <c r="C10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="2:3">
+    <row r="11" spans="2:10">
       <c r="C11" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="2:3">
+    <row r="12" spans="2:10">
       <c r="C12" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="2:3">
+    <row r="13" spans="2:10">
       <c r="C13" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="2:3">
+    <row r="15" spans="2:10">
       <c r="C15" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="2:3">
+    <row r="16" spans="2:10">
       <c r="C16" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="17" spans="3:3">
+      <c r="I16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9">
       <c r="C17" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="18" spans="3:3">
+      <c r="I17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9">
       <c r="C18" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="19" spans="3:3">
+      <c r="I18" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9">
       <c r="C19" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="20" spans="3:3">
+      <c r="I19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9">
       <c r="C20" t="s">
         <v>76</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4"/>
+  <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1412,7 +1497,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4"/>
+  <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1472,7 +1557,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4"/>
+  <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1487,17 +1572,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4f770298-b31c-4238-a90d-db1340869ae4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4ebca473-6c88-4eeb-9b46-7f2093239612" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100D00E93C39DF401468E770D4882DF02E4" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="96f527420be350019f68a523211badd0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4f770298-b31c-4238-a90d-db1340869ae4" xmlns:ns3="4ebca473-6c88-4eeb-9b46-7f2093239612" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="43e7199c2f8c1b8a43238954ae45261b" ns2:_="" ns3:_="">
     <xsd:import namespace="4f770298-b31c-4238-a90d-db1340869ae4"/>
@@ -1704,6 +1778,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4f770298-b31c-4238-a90d-db1340869ae4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4ebca473-6c88-4eeb-9b46-7f2093239612" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDD466A4-E68C-487D-B50D-CD9BB6F63972}">
   <ds:schemaRefs>
@@ -1713,17 +1798,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67695040-79B2-417D-B035-75DD04DAF546}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4f770298-b31c-4238-a90d-db1340869ae4"/>
-    <ds:schemaRef ds:uri="4ebca473-6c88-4eeb-9b46-7f2093239612"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC94E59D-9800-48D6-9A19-37F16AE9BE8D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1740,4 +1814,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67695040-79B2-417D-B035-75DD04DAF546}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4f770298-b31c-4238-a90d-db1340869ae4"/>
+    <ds:schemaRef ds:uri="4ebca473-6c88-4eeb-9b46-7f2093239612"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>